--- a/RePSS_Entreprise_Reference.xlsx
+++ b/RePSS_Entreprise_Reference.xlsx
@@ -722,7 +722,11 @@
           <t>photoCouverture</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>photo_couverture.jpg</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>photo/illustration page de couverture, sous l'encadré nom du chantier (optionnel)</t>
